--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_町データ待ちの切り分け_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_町データ待ちの切り分け_20261019.xlsx
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア者・重症心身障害者を含む）と個別避難計画の作成状況</t>
+          <t>医療的ケア児等の人数と状況（18歳以上の医療的ケア児等・重症心身障害者を含む）と個別避難計画の作成状況</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
